--- a/backend/test_template_export.xlsx
+++ b/backend/test_template_export.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2025-12-15 07:23:25 UTC</t>
+          <t>Generated: 2026-02-24 11:49:24 UTC</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>c6b0fa35-a62d-4cca-8ecf-dbc7da438fb6</t>
+          <t>371f3e9c-8c9c-4445-86fc-db6146ff02e9</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="F2" s="8" t="n">
@@ -843,7 +843,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2e7e89bc-b8e0-4803-b291-b81ac18569d7</t>
+          <t>98eb3e61-61f8-4bea-8051-59bb4e3e2e70</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="F3" s="8" t="n">
@@ -895,7 +895,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>de289272-ca25-4f3e-8a61-865c0f037006</t>
+          <t>4997c0fd-eec9-405f-b0e1-5630a77aaa56</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="F4" s="8" t="n">
@@ -947,7 +947,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>3caf0603-83d3-48ff-8006-fe5c95f88903</t>
+          <t>457b2514-64e2-4405-9449-77e15a0f8261</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="F5" s="8" t="n">
@@ -999,7 +999,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>148aa3a2-07eb-4fc5-bcaa-1d016b3da17f</t>
+          <t>0e06e46f-d1ca-472d-83d9-775db783b206</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="F6" s="8" t="n">
@@ -1051,7 +1051,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>40e6ba40-5887-4daf-96de-36e14331ce72</t>
+          <t>d90685a7-f63b-408f-93f3-0a5a885af054</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="F7" s="8" t="n">
@@ -1103,7 +1103,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>664ff645-a655-436e-a5d3-5a0cc84013b6</t>
+          <t>6ed680f9-c7be-43c5-95df-0700c1499304</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="F8" s="8" t="n">
@@ -1155,7 +1155,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>cf22cd08-e156-4743-9fb8-c297002216b0</t>
+          <t>c4e062b6-3fae-4090-b9e2-2d688434a1c8</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="F9" s="8" t="n">
@@ -1207,7 +1207,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>79c6d6b7-5ef0-4dcd-b5ae-a741fb05d12f</t>
+          <t>aaee8096-ace4-4fc4-ba03-393b58ffcbc6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
@@ -1259,7 +1259,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>1af6b945-13b0-48a7-a836-856e9a5267d8</t>
+          <t>cb88cff5-9a03-42ce-afb6-b2043ab53583</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>2025-12-15 07:23:25</t>
+          <t>2026-02-24 11:49:24</t>
         </is>
       </c>
       <c r="F11" s="8" t="n">
@@ -1985,14 +1985,14 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
+          <t>rebalance_threshold</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
           <t>trigger_threshold</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>rebalance_threshold</t>
-        </is>
-      </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
           <t>max_position_size</t>
@@ -2000,22 +2000,22 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
+          <t>total_return</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
           <t>volatility</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>max_drawdown</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>sharpe_ratio</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>max_drawdown</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>total_return</t>
         </is>
       </c>
     </row>
@@ -2026,25 +2026,25 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.01</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.02</v>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.15</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0.1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2054,25 +2054,25 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.015</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.03</v>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.16</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.1</v>
       </c>
       <c r="G4" t="n">
         <v>0.09000000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="5">
@@ -2082,25 +2082,25 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.02</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.04</v>
       </c>
       <c r="D5" t="n">
         <v>0.2</v>
       </c>
       <c r="E5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.17</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.2</v>
       </c>
       <c r="G5" t="n">
         <v>0.08</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
@@ -2110,25 +2110,25 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.025</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.05</v>
       </c>
       <c r="D6" t="n">
         <v>0.25</v>
       </c>
       <c r="E6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.18</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.3</v>
       </c>
       <c r="G6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.11</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7">
@@ -2138,25 +2138,25 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.03</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.06</v>
       </c>
       <c r="D7" t="n">
         <v>0.3</v>
       </c>
       <c r="E7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.19</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.4</v>
       </c>
       <c r="G7" t="n">
         <v>0.06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.13</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8">
@@ -2166,25 +2166,25 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C8" t="n">
         <v>0.035</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.07000000000000001</v>
       </c>
       <c r="D8" t="n">
         <v>0.35</v>
       </c>
       <c r="E8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F8" t="n">
         <v>0.2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.5</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.15</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -2194,25 +2194,25 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.04</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.08</v>
       </c>
       <c r="D9" t="n">
         <v>0.4</v>
       </c>
       <c r="E9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.21</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.6</v>
       </c>
       <c r="G9" t="n">
         <v>0.04000000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.17</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="10">
@@ -2222,25 +2222,25 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.04500000000000001</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.09000000000000001</v>
       </c>
       <c r="D10" t="n">
         <v>0.4500000000000001</v>
       </c>
       <c r="E10" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.22</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.7</v>
       </c>
       <c r="G10" t="n">
         <v>0.03</v>
       </c>
       <c r="H10" t="n">
-        <v>0.19</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -2250,25 +2250,25 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.05</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.1</v>
       </c>
       <c r="D11" t="n">
         <v>0.5</v>
       </c>
       <c r="E11" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.23</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.8</v>
       </c>
       <c r="G11" t="n">
         <v>0.02</v>
       </c>
       <c r="H11" t="n">
-        <v>0.21</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="12">
@@ -2278,25 +2278,25 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.055</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.11</v>
       </c>
       <c r="D12" t="n">
         <v>0.55</v>
       </c>
       <c r="E12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F12" t="n">
         <v>0.24</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.9</v>
       </c>
       <c r="G12" t="n">
         <v>0.01000000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.23</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
